--- a/data/merged/2026-09-23/MERGED_UK_Wet-Dry-Floor-Washer_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_UK_Wet-Dry-Floor-Washer_2026-09-23.xlsx
@@ -3867,13 +3867,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3955,13 +3955,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4087,13 +4087,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4137,7 +4137,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4225,7 +4225,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4395,13 +4395,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4439,13 +4439,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4489,7 +4489,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4703,13 +4703,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5055,13 +5055,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5122,402 +5122,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId41" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="42" name="Product 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId42" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="43" name="Product 43">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId43" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="44" name="Product 44">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId44" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="45" name="Product 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId45" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Product 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId46" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Product 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="Product 48">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5859,7 +5463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR42"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -7564,7 +7168,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B083M3VH8K</t>
+          <t>B086QLNK2W</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -7577,23 +7181,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Vacmaster Wet &amp; Dry Vacuum Cleaner 30L with Push Clean Filter, 240V L Class Industrial Dust Extractor, 1400W Motor, Power Tak</t>
+          <t>RYOBI 18V ONE+ Wet &amp; Dry Vac (Battery &amp; Charger Excluded)sR18WDV-0, Hyper Green, wet and dry cleaning, washable filter, wor</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B083M3VH8K?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B086QLNK2W?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71PQHoRU8fL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71q6C8hxBzL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B083M3VH8K</t>
+          <t>B086QLNK2W</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7609,14 +7213,12 @@
       <c r="W14" s="15"/>
       <c r="X14" s="15"/>
       <c r="Y14"/>
-      <c r="Z14" s="19">
-        <v>83.32</v>
-      </c>
+      <c r="Z14" s="19"/>
       <c r="AA14"/>
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="20">
-        <v>124</v>
+        <v>213</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="21">
@@ -7672,7 +7274,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B086QLNK2W</t>
+          <t>B098B82K8D</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -7685,23 +7287,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>RYOBI 18V ONE+ Wet &amp; Dry Vac (Battery &amp; Charger Excluded)sR18WDV-0, Hyper Green, wet and dry cleaning, washable filter, wor</t>
+          <t>WORX WX031.9 20V Cordless Wet/Dry Vacuums20V wet/dry vacuum; lightweight &amp; portable</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B086QLNK2W?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B098B82K8D?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71q6C8hxBzL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/714aUu7a7LL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B086QLNK2W</t>
+          <t>B098B82K8D</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7717,16 +7319,18 @@
       <c r="W15" s="15"/>
       <c r="X15" s="15"/>
       <c r="Y15"/>
-      <c r="Z15" s="19"/>
+      <c r="Z15" s="19">
+        <v>91.66</v>
+      </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="20">
-        <v>213</v>
+        <v>359</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG15" s="22">
         <v>0</v>
@@ -7778,7 +7382,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B08PC6FMY3</t>
+          <t>B09CLDC89W</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -7791,23 +7395,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Evolution Power Tools R15VAC Vacuum Cleaner Wet and Dry Vac, Portable and Lightweight Ideal Dust Extractor for Saw Dust in Wo</t>
+          <t>Bosch Cordless Wet and Dry Vacuum Cleaner AdvancedVac 18V-8 (Without Battery, 18 Volt System, Accessory Set Included, in Cart</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B08PC6FMY3?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09CLDC89W?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51YRW14YWGL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71RsLGatnXL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B08PC6FMY3</t>
+          <t>B09CLDC89W</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7824,17 +7428,17 @@
       <c r="X16" s="15"/>
       <c r="Y16"/>
       <c r="Z16" s="19">
-        <v>66.67</v>
+        <v>81.54</v>
       </c>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="20">
-        <v>759</v>
+        <v>629</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="21">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AG16" s="22">
         <v>0</v>
@@ -7886,7 +7490,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B098B82K8D</t>
+          <t>B09NMKXV6T</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -7899,23 +7503,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>WORX WX031.9 20V Cordless Wet/Dry Vacuums20V wet/dry vacuum; lightweight &amp; portable</t>
+          <t>KÄRCHER 16283020 Wet &amp; Dry Vacuum Cleaner WD 5, Blower Function, Power: 1100w, Plastic Container: 25 L, Suction Hose: 2.2 M,</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B098B82K8D?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09NMKXV6T?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/714aUu7a7LL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61Xm8VXEUEL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B098B82K8D</t>
+          <t>B09NMKXV6T</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7932,13 +7536,13 @@
       <c r="X17" s="15"/>
       <c r="Y17"/>
       <c r="Z17" s="19">
-        <v>91.66</v>
+        <v>122.32</v>
       </c>
       <c r="AA17"/>
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="20">
-        <v>359</v>
+        <v>312</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="21">
@@ -7994,7 +7598,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B09CLDC89W</t>
+          <t>B0B29GRWSR</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -8007,23 +7611,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Bosch Cordless Wet and Dry Vacuum Cleaner AdvancedVac 18V-8 (Without Battery, 18 Volt System, Accessory Set Included, in Cart</t>
+          <t>HYUNDAI 1200W 25L 2-in-1 Upholstery and Carpet Cleaner Wet &amp; Dry Vacuum for Home, Car Seats, Carpets and Hard Floors</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09CLDC89W?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0B29GRWSR?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71RsLGatnXL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61PIkv1618L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B09CLDC89W</t>
+          <t>B0B29GRWSR</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8040,17 +7644,17 @@
       <c r="X18" s="15"/>
       <c r="Y18"/>
       <c r="Z18" s="19">
-        <v>81.54</v>
+        <v>87.49</v>
       </c>
       <c r="AA18"/>
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="20">
-        <v>629</v>
+        <v>225</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG18" s="22">
         <v>0</v>
@@ -8102,7 +7706,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B09NMKHHLN</t>
+          <t>B0B4NSXDHS</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8115,23 +7719,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER WD 3 Wet and Dry Vacuum Cleaner, 17 LsCartridge Filter, Plastic Container: 17 L, Suction Hose: 2 m and Hose Storage</t>
+          <t>Swan Dirtmaster Crossover All-in-One Wet Dry Vacuum Cleaner, Multi-Surface Hard floors and Carpets, Cordless, LED Display, Vo</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09NMKHHLN?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0B4NSXDHS?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51Hc6WvljUL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51w4u6UbFuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B09NMKHHLN</t>
+          <t>B0B4NSXDHS</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8147,18 +7751,16 @@
       <c r="W19" s="15"/>
       <c r="X19" s="15"/>
       <c r="Y19"/>
-      <c r="Z19" s="19">
-        <v>65.83</v>
-      </c>
+      <c r="Z19" s="19"/>
       <c r="AA19"/>
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="20">
-        <v>838</v>
+        <v>146</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
@@ -8210,7 +7812,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B09NMKVGNT</t>
+          <t>B0BVRQSDT6</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8223,23 +7825,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER WD 2 Plus Wet and Dry Vacuum Cleaner, 12 LsBlowing function, power: 1000w, cartridge filter, floor and crevice nozz</t>
+          <t>Vax Glide 2 Cordless Hard Floor Cleaner, Wash, Deep Clean and Dry Spills and Stains in the Home, Lightweight and Powerful wit</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09NMKVGNT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0BVRQSDT6?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51H5+g5PHJL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61dukUaJDML._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B09NMKVGNT</t>
+          <t>B0BVRQSDT6</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8255,18 +7857,16 @@
       <c r="W20" s="15"/>
       <c r="X20" s="15"/>
       <c r="Y20"/>
-      <c r="Z20" s="19">
-        <v>50.83</v>
-      </c>
+      <c r="Z20" s="19"/>
       <c r="AA20"/>
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="20">
-        <v>2670</v>
+        <v>98</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="21">
-        <v>4.6</v>
+        <v>3.5</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
@@ -8318,7 +7918,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B09NMKXV6T</t>
+          <t>B0CCRTVTWB</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8331,23 +7931,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER 16283020 Wet &amp; Dry Vacuum Cleaner WD 5, Blower Function, Power: 1100w, Plastic Container: 25 L, Suction Hose: 2.2 M,</t>
+          <t>RYOBI 18V ONE+ Wet &amp; Dry Project Vac (Battery &amp; Charger Excluded)sRV1811-0, Hyper Green, 11L tank, wet and dry cleaning, wo</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09NMKXV6T?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CCRTVTWB?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61Xm8VXEUEL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Z49VI1-QL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B09NMKXV6T</t>
+          <t>B0CCRTVTWB</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8363,18 +7963,16 @@
       <c r="W21" s="15"/>
       <c r="X21" s="15"/>
       <c r="Y21"/>
-      <c r="Z21" s="19">
-        <v>122.32</v>
-      </c>
+      <c r="Z21" s="19"/>
       <c r="AA21"/>
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="20">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
@@ -8426,7 +8024,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0B29GRWSR</t>
+          <t>B0CFVBTCGR</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8439,23 +8037,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>HYUNDAI 1200W 25L 2-in-1 Upholstery and Carpet Cleaner Wet &amp; Dry Vacuum for Home, Car Seats, Carpets and Hard Floors</t>
+          <t>Shark HydroVac Cordless Hard Floor Cleaner Grey WD210UKsAntimicrobial Brush-Roll, Odour-Neutralising Multi-Surface Solution</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0B29GRWSR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CFVBTCGR?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61PIkv1618L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61G1CZpYmAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0B29GRWSR</t>
+          <t>B0CFVBTCGR</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8471,18 +8069,16 @@
       <c r="W22" s="15"/>
       <c r="X22" s="15"/>
       <c r="Y22"/>
-      <c r="Z22" s="19">
-        <v>87.49</v>
-      </c>
+      <c r="Z22" s="19"/>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="20">
-        <v>225</v>
+        <v>278</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="21">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -8534,7 +8130,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0B4NSXDHS</t>
+          <t>B0CLJB2BPC</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8547,23 +8143,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Swan Dirtmaster Crossover All-in-One Wet Dry Vacuum Cleaner, Multi-Surface Hard floors and Carpets, Cordless, LED Display, Vo</t>
+          <t>DEWALTsWet &amp; Dry Vacuum | 1050W 20 Litre 240V Capacity | DXV20PA | Powerful 15kPa suction with blower function, water-resis</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0B4NSXDHS?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CLJB2BPC?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51w4u6UbFuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/41a9lM1zxaL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0B4NSXDHS</t>
+          <t>B0CLJB2BPC</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8584,11 +8180,11 @@
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="20">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="21">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -8640,7 +8236,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0BBVY1LB4</t>
+          <t>B0CMC4GYR8</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8653,23 +8249,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>DEWALT UKADXV23P, Wet Dry Vacuum, Yellow+Black, 1150 W, 23 liters</t>
+          <t>WORKPRO 1200 W 20 L Wet and Dry Vacuum Cleaner with HEPA &amp; Blowers3-in-1 Blower Function, Stainless Steel Tank, Dust Extrac</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0BBVY1LB4?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CMC4GYR8?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61piWzDzo8L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71BKlalgYAL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0BBVY1LB4</t>
+          <t>B0CMC4GYR8</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8690,11 +8286,11 @@
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="20">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="21">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AG24" s="22">
         <v>0</v>
@@ -8746,7 +8342,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0BGNLL563</t>
+          <t>B0CNGZQD6B</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8759,23 +8355,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER WD 6 P Wet and Dry Vacuum Cleaner, 30L Stainless Steel + Power Socket</t>
+          <t>dreame H12 Pro Wet Dry Vacuum CleanersSmart Dirt Detection, Hot Air Self-Drying, Anti-Hair Tangle, Includes 500ml Cleaning</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0BGNLL563?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CNGZQD6B?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71o7Kk6f0YL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/617n3IksnHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0BGNLL563</t>
+          <t>B0CNGZQD6B</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8791,18 +8387,16 @@
       <c r="W25" s="15"/>
       <c r="X25" s="15"/>
       <c r="Y25"/>
-      <c r="Z25" s="19">
-        <v>174.99</v>
-      </c>
+      <c r="Z25" s="19"/>
       <c r="AA25"/>
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="20">
-        <v>140</v>
+        <v>109</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="21">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -8854,7 +8448,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0BVRQSDT6</t>
+          <t>B0CRRG5HVX</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8867,23 +8461,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>Vax Glide 2 Cordless Hard Floor Cleaner, Wash, Deep Clean and Dry Spills and Stains in the Home, Lightweight and Powerful wit</t>
+          <t>Tineco iFLOOR 5 Breeze Complete Wet Dry Vacuum Cordless Floor Washer, One-Step Cleaning for Hard Floors, Edge Clean, Auto Sel</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0BVRQSDT6?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CRRG5HVX?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61dukUaJDML._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/615aD+03D3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0BVRQSDT6</t>
+          <t>B0CRRG5HVX</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8904,11 +8498,11 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="20">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="21">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -8960,7 +8554,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0CCRTVTWB</t>
+          <t>B0CV5L22GW</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8973,23 +8567,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>RYOBI 18V ONE+ Wet &amp; Dry Project Vac (Battery &amp; Charger Excluded)sRV1811-0, Hyper Green, 11L tank, wet and dry cleaning, wo</t>
+          <t>Beldray All-in-One Floor Cleaner – 180W 3-in-1 Cordless Vacuum, Mop &amp; Dry Cleaner, Multi-Surface Wet/Dry Electric Mop, Self-C</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CCRTVTWB?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CV5L22GW?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Z49VI1-QL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51wD3krd5pL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0CCRTVTWB</t>
+          <t>B0CV5L22GW</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -9010,11 +8604,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="20">
-        <v>286</v>
+        <v>131</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="21">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -9066,7 +8660,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0CFVBTCGR</t>
+          <t>B0CVX37Y93</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9079,23 +8673,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Shark HydroVac Cordless Hard Floor Cleaner Grey WD210UKsAntimicrobial Brush-Roll, Odour-Neutralising Multi-Surface Solution</t>
+          <t>Tineco Floor ONE STRETCH S6 Cordless Wet Dry Vacuum Cleaner, 180°Lay-flat Smart Vacuum Mop, 13cm Compact Design, 70℃ Flashdry</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CFVBTCGR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CVX37Y93?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61G1CZpYmAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71a2hp5QU4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0CFVBTCGR</t>
+          <t>B0CVX37Y93</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9116,11 +8710,11 @@
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="20">
-        <v>278</v>
+        <v>823</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -9172,7 +8766,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0CLJB2BPC</t>
+          <t>B0DJVWGQX1</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9185,23 +8779,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>DEWALTsWet &amp; Dry Vacuum | 1050W 20 Litre 240V Capacity | DXV20PA | Powerful 15kPa suction with blower function, water-resis</t>
+          <t>metabo ASA 30 M PC (602087380) 30L M-Class Wet &amp; Dry All Purpose Vaccum Cleaner, 240V / 1200W</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CLJB2BPC?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DJVWGQX1?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/41a9lM1zxaL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51w6h2F2dwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0CLJB2BPC</t>
+          <t>B0DJVWGQX1</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9222,11 +8816,11 @@
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="20">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="21">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -9278,7 +8872,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0CMC4GYR8</t>
+          <t>B0DPGJ8NTW</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9291,23 +8885,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>WORKPRO 1200 W 20 L Wet and Dry Vacuum Cleaner with HEPA &amp; Blowers3-in-1 Blower Function, Stainless Steel Tank, Dust Extrac</t>
+          <t>BISSELL CrossWave OmniForce Edge Cordless Wet-Dry Vacuum Cleaner 4017EsPowerful floor cleaner with ZeroGap™ Tech, edge-to-e</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CMC4GYR8?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DPGJ8NTW?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71BKlalgYAL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/51hO3VO8sgL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0CMC4GYR8</t>
+          <t>B0DPGJ8NTW</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9328,11 +8922,11 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="20">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="21">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -9384,7 +8978,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0CNGZQD6B</t>
+          <t>B0DWFZ1GWR</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9397,23 +8991,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>dreame H12 Pro Wet Dry Vacuum CleanersSmart Dirt Detection, Hot Air Self-Drying, Anti-Hair Tangle, Includes 500ml Cleaning</t>
+          <t>Compatible Titan (3m) Wet &amp; Dry Vacuum Cleaner Hose (35mm Fitting)swith Swivel Cuff for Titan TTB774VAC, TTB775VAC, TTB776V</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CNGZQD6B?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DWFZ1GWR?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/617n3IksnHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71W7kv60oTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0CNGZQD6B</t>
+          <t>B0DWFZ1GWR</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9434,11 +9028,11 @@
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="20">
-        <v>109</v>
+        <v>33</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="21">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -9490,7 +9084,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0CNRT2132</t>
+          <t>B0F54PJHNV</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9503,23 +9097,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER WD 4 Wet &amp; Dry Vacuum Cleaner, 20 LsPower: 1000W, plastic container: 20l, suction hose: 2.2m, blower function, flat</t>
+          <t>Ark Mat WET AND DRY VACUUM CLEANER with Blow Function 10L - Lightweight 2.5kg Wet Dry Hoover with 800W Suction Power, Include</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CNRT2132?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F54PJHNV?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61ooDYkz3gL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71jUHr7KHeL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0CNRT2132</t>
+          <t>B0F54PJHNV</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9535,18 +9129,16 @@
       <c r="W32" s="15"/>
       <c r="X32" s="15"/>
       <c r="Y32"/>
-      <c r="Z32" s="19">
-        <v>82.5</v>
-      </c>
+      <c r="Z32" s="19"/>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="20">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
@@ -9598,7 +9190,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0CRRG5HVX</t>
+          <t>B0F7JY3BHY</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9611,23 +9203,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Tineco iFLOOR 5 Breeze Complete Wet Dry Vacuum Cordless Floor Washer, One-Step Cleaning for Hard Floors, Edge Clean, Auto Sel</t>
+          <t>Tineco FLOOR ONE i5 Stretch Cordless Hard Floor Wet Dry Vacuum Cleaner and Mop, 180° Lay-flat Design, for Hardwood, Tile, 20k</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CRRG5HVX?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F7JY3BHY?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/615aD+03D3L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61L+f7jvShL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0CRRG5HVX</t>
+          <t>B0F7JY3BHY</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9648,11 +9240,11 @@
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="20">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="21">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
@@ -9704,7 +9296,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0CV5L22GW</t>
+          <t>B0FLJDDWQM</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9717,23 +9309,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Beldray All-in-One Floor Cleaner – 180W 3-in-1 Cordless Vacuum, Mop &amp; Dry Cleaner, Multi-Surface Wet/Dry Electric Mop, Self-C</t>
+          <t>Einhell Wet and Dry Vacuum Cleaner 900W 15L Stainless Steel Tanks180 Mbar Suction Capacity Accessory Bracket including Vari</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CV5L22GW?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FLJDDWQM?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51wD3krd5pL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61PF6yf8UEL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0CV5L22GW</t>
+          <t>B0FLJDDWQM</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9749,16 +9341,18 @@
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
       <c r="Y34"/>
-      <c r="Z34" s="19"/>
+      <c r="Z34" s="19">
+        <v>33.32</v>
+      </c>
       <c r="AA34"/>
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="20">
-        <v>131</v>
+        <v>18</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="21">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
@@ -9810,7 +9404,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0CVX37Y93</t>
+          <t>B0FQJS7TKK</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9823,23 +9417,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Tineco Floor ONE STRETCH S6 Cordless Wet Dry Vacuum Cleaner, 180°Lay-flat Smart Vacuum Mop, 13cm Compact Design, 70℃ Flashdry</t>
+          <t>Einhell Wet and Dry Vacuum Cleaner 900W 20L Stainless Steel Tanks180 mbar Suction Capacity, Accessory Bracket Including Var</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CVX37Y93?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FQJS7TKK?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71a2hp5QU4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71A25KhrmQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0CVX37Y93</t>
+          <t>B0FQJS7TKK</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9855,16 +9449,18 @@
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35"/>
-      <c r="Z35" s="19"/>
+      <c r="Z35" s="19">
+        <v>40.82</v>
+      </c>
       <c r="AA35"/>
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="20">
-        <v>823</v>
+        <v>79</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="21">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
@@ -9916,7 +9512,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0DJVWGQX1</t>
+          <t>B0FWQK9J67</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9929,23 +9525,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>metabo ASA 30 M PC (602087380) 30L M-Class Wet &amp; Dry All Purpose Vaccum Cleaner, 240V / 1200W</t>
+          <t>15L Industrial Wet Dry Vacuum Cleaner with 4 Caster Wheels, 2000W Motor Professional Electric Wet Dry Vac, Bagless, 19000pa P</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DJVWGQX1?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FWQK9J67?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51w6h2F2dwL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71QQSYxzFRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0DJVWGQX1</t>
+          <t>B0FWQK9J67</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9966,11 +9562,11 @@
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="21">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="AG36" s="22">
         <v>0</v>
@@ -10022,7 +9618,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0DPGJ8NTW</t>
+          <t>B0FZDZCB3J</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10035,23 +9631,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>BISSELL CrossWave OmniForce Edge Cordless Wet-Dry Vacuum Cleaner 4017EsPowerful floor cleaner with ZeroGap™ Tech, edge-to-e</t>
+          <t>HomeTronix 30L Wet &amp; Dry Vacuum Cleaner Powerful SuctionsStainless Steel Tank | HEPA Filter | 10M Cable | Quiet ≤80dB | For</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DPGJ8NTW?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FZDZCB3J?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51hO3VO8sgL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61mDGPAy6RL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0DPGJ8NTW</t>
+          <t>B0FZDZCB3J</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10072,11 +9668,11 @@
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="20">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="21">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="AG37" s="22">
         <v>0</v>
@@ -10128,7 +9724,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0DWFZ1GWR</t>
+          <t>B0G2KSRMM3</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10141,23 +9737,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Compatible Titan (3m) Wet &amp; Dry Vacuum Cleaner Hose (35mm Fitting)swith Swivel Cuff for Titan TTB774VAC, TTB775VAC, TTB776V</t>
+          <t>Tineco FLOOR ONE S9 Master Wet Dry Vacuum Cleaner, StreakFree Scraper, ThermoBlast Tech, Hot Water Mopping, 9.9cm Ultra-Slim</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DWFZ1GWR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0G2KSRMM3?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71W7kv60oTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61zSPayhZhL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0DWFZ1GWR</t>
+          <t>B0G2KSRMM3</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10178,11 +9774,11 @@
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="20">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="21">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AG38" s="22">
         <v>0</v>
@@ -10234,7 +9830,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0F54PJHNV</t>
+          <t>B0G4BQN2R8</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10247,23 +9843,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Ark Mat WET AND DRY VACUUM CLEANER with Blow Function 10L - Lightweight 2.5kg Wet Dry Hoover with 800W Suction Power, Include</t>
+          <t>HOMCOM 3-in-1 Wet and Dry Vacuum Cleaner 1200W Blowing Mode 20L YellowsStainless Steel Tank, Triple Filters, Crevice Nozzle</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F54PJHNV?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0G4BQN2R8?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71jUHr7KHeL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Hnmdt4DPL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0F54PJHNV</t>
+          <t>B0G4BQN2R8</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10284,11 +9880,11 @@
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="20">
-        <v>103</v>
+        <v>17</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="21">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AG39" s="22">
         <v>0</v>
@@ -10340,7 +9936,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0F7JY3BHY</t>
+          <t>B0GFWYBKND</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10353,23 +9949,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Tineco FLOOR ONE i5 Stretch Cordless Hard Floor Wet Dry Vacuum Cleaner and Mop, 180° Lay-flat Design, for Hardwood, Tile, 20k</t>
+          <t>BISSELL CrossWave EdgeFind Wet &amp; Dry Vacuum Cleaner 4136EsPowerful multi-surface pet mess cleanup with ZeroGap Technology,</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F7JY3BHY?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GFWYBKND?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61L+f7jvShL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61XkhLLFv3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0F7JY3BHY</t>
+          <t>B0GFWYBKND</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10385,16 +9981,18 @@
       <c r="W40" s="15"/>
       <c r="X40" s="15"/>
       <c r="Y40"/>
-      <c r="Z40" s="19"/>
+      <c r="Z40" s="19">
+        <v>165.83</v>
+      </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="20">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="21">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="AG40" s="22">
         <v>0</v>
@@ -10446,7 +10044,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0FLJDDWQM</t>
+          <t>B0GQMKR2TW</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10459,23 +10057,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Einhell Wet and Dry Vacuum Cleaner 900W 15L Stainless Steel Tanks180 Mbar Suction Capacity Accessory Bracket including Vari</t>
+          <t>Vehiwell Cordless Wet and Dry Vacuum Cleaners3-in-1 Industrial Brushed Vacuum Cleaner, 10L Dry+ 5L Wet Capacity, 13 kPa Suc</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FLJDDWQM?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GQMKR2TW?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61PF6yf8UEL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/7166tI1-FbL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0FLJDDWQM</t>
+          <t>B0GQMKR2TW</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10491,18 +10089,16 @@
       <c r="W41" s="15"/>
       <c r="X41" s="15"/>
       <c r="Y41"/>
-      <c r="Z41" s="19">
-        <v>33.32</v>
-      </c>
+      <c r="Z41" s="19"/>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="20">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="21">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG41" s="22">
         <v>0</v>
@@ -10554,7 +10150,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0FQJS7TKK</t>
+          <t>B0HFYQ6RK2</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10567,23 +10163,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Einhell Wet and Dry Vacuum Cleaner 900W 20L Stainless Steel Tanks180 mbar Suction Capacity, Accessory Bracket Including Var</t>
+          <t>VORACIS 2000W Wet &amp; Dry Vacuum Cleaners20L Stainless Steel | 18000Pa Suction | Blower | HEPA Filter | Car, Home &amp; Garage</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FQJS7TKK?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HFYQ6RK2?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71A25KhrmQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71VX3s1TU3L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0FQJS7TKK</t>
+          <t>B0HFYQ6RK2</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10599,19 +10195,13 @@
       <c r="W42" s="15"/>
       <c r="X42" s="15"/>
       <c r="Y42"/>
-      <c r="Z42" s="19">
-        <v>40.82</v>
-      </c>
+      <c r="Z42" s="19"/>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42"/>
-      <c r="AD42" s="20">
-        <v>79</v>
-      </c>
+      <c r="AD42" s="20"/>
       <c r="AE42"/>
-      <c r="AF42" s="21">
-        <v>4</v>
-      </c>
+      <c r="AF42" s="21"/>
       <c r="AG42" s="22">
         <v>0</v>
       </c>
@@ -10654,960 +10244,6 @@
       <c r="BP42"/>
       <c r="BQ42" s="23"/>
       <c r="BR42"/>
-    </row>
-    <row r="43" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="13">
-        <v>42</v>
-      </c>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14" t="inlineStr">
-        <is>
-          <t>B0FWQK9J67</t>
-        </is>
-      </c>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43"/>
-      <c r="G43" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>15L Industrial Wet Dry Vacuum Cleaner with 4 Caster Wheels, 2000W Motor Professional Electric Wet Dry Vac, Bagless, 19000pa P</t>
-        </is>
-      </c>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0FWQK9J67?psc=1</t>
-        </is>
-      </c>
-      <c r="K43" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71QQSYxzFRL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L43" s="14" t="inlineStr">
-        <is>
-          <t>B0FWQK9J67</t>
-        </is>
-      </c>
-      <c r="M43" s="1"/>
-      <c r="N43" s="14"/>
-      <c r="O43" s="15"/>
-      <c r="P43" s="15"/>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="18"/>
-      <c r="T43" s="15"/>
-      <c r="U43" s="16"/>
-      <c r="V43" s="15"/>
-      <c r="W43" s="15"/>
-      <c r="X43" s="15"/>
-      <c r="Y43"/>
-      <c r="Z43" s="19"/>
-      <c r="AA43"/>
-      <c r="AB43"/>
-      <c r="AC43"/>
-      <c r="AD43" s="20">
-        <v>10</v>
-      </c>
-      <c r="AE43"/>
-      <c r="AF43" s="21">
-        <v>3.6</v>
-      </c>
-      <c r="AG43" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH43"/>
-      <c r="AI43" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ43"/>
-      <c r="AK43" s="1"/>
-      <c r="AL43" s="20"/>
-      <c r="AM43"/>
-      <c r="AN43" s="13"/>
-      <c r="AO43" s="13"/>
-      <c r="AP43"/>
-      <c r="AQ43" s="20"/>
-      <c r="AR43"/>
-      <c r="AS43"/>
-      <c r="AT43"/>
-      <c r="AU43" s="13"/>
-      <c r="AV43" s="14"/>
-      <c r="AW43" s="13"/>
-      <c r="AX43" s="13"/>
-      <c r="AY43" s="13"/>
-      <c r="AZ43" s="13"/>
-      <c r="BA43" s="13"/>
-      <c r="BB43" s="13"/>
-      <c r="BC43" s="13"/>
-      <c r="BD43" s="13"/>
-      <c r="BE43" s="13"/>
-      <c r="BF43" s="13"/>
-      <c r="BG43" s="13"/>
-      <c r="BH43" s="14"/>
-      <c r="BI43"/>
-      <c r="BJ43"/>
-      <c r="BK43" s="23"/>
-      <c r="BL43"/>
-      <c r="BM43" s="23"/>
-      <c r="BN43"/>
-      <c r="BO43" s="23"/>
-      <c r="BP43"/>
-      <c r="BQ43" s="23"/>
-      <c r="BR43"/>
-    </row>
-    <row r="44" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="13">
-        <v>43</v>
-      </c>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14" t="inlineStr">
-        <is>
-          <t>B0FZDZCB3J</t>
-        </is>
-      </c>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44"/>
-      <c r="G44" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>HomeTronix 30L Wet &amp; Dry Vacuum Cleaner Powerful SuctionsStainless Steel Tank | HEPA Filter | 10M Cable | Quiet ≤80dB | For</t>
-        </is>
-      </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0FZDZCB3J?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61mDGPAy6RL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="14" t="inlineStr">
-        <is>
-          <t>B0FZDZCB3J</t>
-        </is>
-      </c>
-      <c r="M44" s="1"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="15"/>
-      <c r="P44" s="15"/>
-      <c r="Q44" s="16"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="18"/>
-      <c r="T44" s="15"/>
-      <c r="U44" s="16"/>
-      <c r="V44" s="15"/>
-      <c r="W44" s="15"/>
-      <c r="X44" s="15"/>
-      <c r="Y44"/>
-      <c r="Z44" s="19"/>
-      <c r="AA44"/>
-      <c r="AB44"/>
-      <c r="AC44"/>
-      <c r="AD44" s="20">
-        <v>26</v>
-      </c>
-      <c r="AE44"/>
-      <c r="AF44" s="21">
-        <v>3.6</v>
-      </c>
-      <c r="AG44" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH44"/>
-      <c r="AI44" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="1"/>
-      <c r="AL44" s="20"/>
-      <c r="AM44"/>
-      <c r="AN44" s="13"/>
-      <c r="AO44" s="13"/>
-      <c r="AP44"/>
-      <c r="AQ44" s="20"/>
-      <c r="AR44"/>
-      <c r="AS44"/>
-      <c r="AT44"/>
-      <c r="AU44" s="13"/>
-      <c r="AV44" s="14"/>
-      <c r="AW44" s="13"/>
-      <c r="AX44" s="13"/>
-      <c r="AY44" s="13"/>
-      <c r="AZ44" s="13"/>
-      <c r="BA44" s="13"/>
-      <c r="BB44" s="13"/>
-      <c r="BC44" s="13"/>
-      <c r="BD44" s="13"/>
-      <c r="BE44" s="13"/>
-      <c r="BF44" s="13"/>
-      <c r="BG44" s="13"/>
-      <c r="BH44" s="14"/>
-      <c r="BI44"/>
-      <c r="BJ44"/>
-      <c r="BK44" s="23"/>
-      <c r="BL44"/>
-      <c r="BM44" s="23"/>
-      <c r="BN44"/>
-      <c r="BO44" s="23"/>
-      <c r="BP44"/>
-      <c r="BQ44" s="23"/>
-      <c r="BR44"/>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="13">
-        <v>44</v>
-      </c>
-      <c r="B45" s="13"/>
-      <c r="C45" s="14" t="inlineStr">
-        <is>
-          <t>B0G2KSRMM3</t>
-        </is>
-      </c>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45"/>
-      <c r="G45" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>Tineco FLOOR ONE S9 Master Wet Dry Vacuum Cleaner, StreakFree Scraper, ThermoBlast Tech, Hot Water Mopping, 9.9cm Ultra-Slim</t>
-        </is>
-      </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0G2KSRMM3?psc=1</t>
-        </is>
-      </c>
-      <c r="K45" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61zSPayhZhL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L45" s="14" t="inlineStr">
-        <is>
-          <t>B0G2KSRMM3</t>
-        </is>
-      </c>
-      <c r="M45" s="1"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="15"/>
-      <c r="P45" s="15"/>
-      <c r="Q45" s="16"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="18"/>
-      <c r="T45" s="15"/>
-      <c r="U45" s="16"/>
-      <c r="V45" s="15"/>
-      <c r="W45" s="15"/>
-      <c r="X45" s="15"/>
-      <c r="Y45"/>
-      <c r="Z45" s="19"/>
-      <c r="AA45"/>
-      <c r="AB45"/>
-      <c r="AC45"/>
-      <c r="AD45" s="20">
-        <v>5</v>
-      </c>
-      <c r="AE45"/>
-      <c r="AF45" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG45" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH45"/>
-      <c r="AI45" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="1"/>
-      <c r="AL45" s="20"/>
-      <c r="AM45"/>
-      <c r="AN45" s="13"/>
-      <c r="AO45" s="13"/>
-      <c r="AP45"/>
-      <c r="AQ45" s="20"/>
-      <c r="AR45"/>
-      <c r="AS45"/>
-      <c r="AT45"/>
-      <c r="AU45" s="13"/>
-      <c r="AV45" s="14"/>
-      <c r="AW45" s="13"/>
-      <c r="AX45" s="13"/>
-      <c r="AY45" s="13"/>
-      <c r="AZ45" s="13"/>
-      <c r="BA45" s="13"/>
-      <c r="BB45" s="13"/>
-      <c r="BC45" s="13"/>
-      <c r="BD45" s="13"/>
-      <c r="BE45" s="13"/>
-      <c r="BF45" s="13"/>
-      <c r="BG45" s="13"/>
-      <c r="BH45" s="14"/>
-      <c r="BI45"/>
-      <c r="BJ45"/>
-      <c r="BK45" s="23"/>
-      <c r="BL45"/>
-      <c r="BM45" s="23"/>
-      <c r="BN45"/>
-      <c r="BO45" s="23"/>
-      <c r="BP45"/>
-      <c r="BQ45" s="23"/>
-      <c r="BR45"/>
-    </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="13">
-        <v>45</v>
-      </c>
-      <c r="B46" s="13"/>
-      <c r="C46" s="14" t="inlineStr">
-        <is>
-          <t>B0G4BQN2R8</t>
-        </is>
-      </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46"/>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>HOMCOM 3-in-1 Wet and Dry Vacuum Cleaner 1200W Blowing Mode 20L YellowsStainless Steel Tank, Triple Filters, Crevice Nozzle</t>
-        </is>
-      </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0G4BQN2R8?psc=1</t>
-        </is>
-      </c>
-      <c r="K46" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Hnmdt4DPL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L46" s="14" t="inlineStr">
-        <is>
-          <t>B0G4BQN2R8</t>
-        </is>
-      </c>
-      <c r="M46" s="1"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="15"/>
-      <c r="P46" s="15"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="18"/>
-      <c r="T46" s="15"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="15"/>
-      <c r="W46" s="15"/>
-      <c r="X46" s="15"/>
-      <c r="Y46"/>
-      <c r="Z46" s="19"/>
-      <c r="AA46"/>
-      <c r="AB46"/>
-      <c r="AC46"/>
-      <c r="AD46" s="20">
-        <v>17</v>
-      </c>
-      <c r="AE46"/>
-      <c r="AF46" s="21">
-        <v>3.8</v>
-      </c>
-      <c r="AG46" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH46"/>
-      <c r="AI46" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ46"/>
-      <c r="AK46" s="1"/>
-      <c r="AL46" s="20"/>
-      <c r="AM46"/>
-      <c r="AN46" s="13"/>
-      <c r="AO46" s="13"/>
-      <c r="AP46"/>
-      <c r="AQ46" s="20"/>
-      <c r="AR46"/>
-      <c r="AS46"/>
-      <c r="AT46"/>
-      <c r="AU46" s="13"/>
-      <c r="AV46" s="14"/>
-      <c r="AW46" s="13"/>
-      <c r="AX46" s="13"/>
-      <c r="AY46" s="13"/>
-      <c r="AZ46" s="13"/>
-      <c r="BA46" s="13"/>
-      <c r="BB46" s="13"/>
-      <c r="BC46" s="13"/>
-      <c r="BD46" s="13"/>
-      <c r="BE46" s="13"/>
-      <c r="BF46" s="13"/>
-      <c r="BG46" s="13"/>
-      <c r="BH46" s="14"/>
-      <c r="BI46"/>
-      <c r="BJ46"/>
-      <c r="BK46" s="23"/>
-      <c r="BL46"/>
-      <c r="BM46" s="23"/>
-      <c r="BN46"/>
-      <c r="BO46" s="23"/>
-      <c r="BP46"/>
-      <c r="BQ46" s="23"/>
-      <c r="BR46"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="13">
-        <v>46</v>
-      </c>
-      <c r="B47" s="13"/>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>B0G7T8PCM4</t>
-        </is>
-      </c>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47"/>
-      <c r="G47" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>DEKO Wet &amp; Dry Vacuum Cleaner: Wet and Dry Vacuum with 16KPA Suction, 10L Large Capacity, Lightweight Industrial Vacuum Clean</t>
-        </is>
-      </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0G7T8PCM4?psc=1</t>
-        </is>
-      </c>
-      <c r="K47" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71JgbgU+z-L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L47" s="14" t="inlineStr">
-        <is>
-          <t>B0G7T8PCM4</t>
-        </is>
-      </c>
-      <c r="M47" s="1"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="15"/>
-      <c r="P47" s="15"/>
-      <c r="Q47" s="16"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="18"/>
-      <c r="T47" s="15"/>
-      <c r="U47" s="16"/>
-      <c r="V47" s="15"/>
-      <c r="W47" s="15"/>
-      <c r="X47" s="15"/>
-      <c r="Y47"/>
-      <c r="Z47" s="19"/>
-      <c r="AA47"/>
-      <c r="AB47"/>
-      <c r="AC47"/>
-      <c r="AD47" s="20">
-        <v>16</v>
-      </c>
-      <c r="AE47"/>
-      <c r="AF47" s="21">
-        <v>3.9</v>
-      </c>
-      <c r="AG47" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH47"/>
-      <c r="AI47" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ47"/>
-      <c r="AK47" s="1"/>
-      <c r="AL47" s="20"/>
-      <c r="AM47"/>
-      <c r="AN47" s="13"/>
-      <c r="AO47" s="13"/>
-      <c r="AP47"/>
-      <c r="AQ47" s="20"/>
-      <c r="AR47"/>
-      <c r="AS47"/>
-      <c r="AT47"/>
-      <c r="AU47" s="13"/>
-      <c r="AV47" s="14"/>
-      <c r="AW47" s="13"/>
-      <c r="AX47" s="13"/>
-      <c r="AY47" s="13"/>
-      <c r="AZ47" s="13"/>
-      <c r="BA47" s="13"/>
-      <c r="BB47" s="13"/>
-      <c r="BC47" s="13"/>
-      <c r="BD47" s="13"/>
-      <c r="BE47" s="13"/>
-      <c r="BF47" s="13"/>
-      <c r="BG47" s="13"/>
-      <c r="BH47" s="14"/>
-      <c r="BI47"/>
-      <c r="BJ47"/>
-      <c r="BK47" s="23"/>
-      <c r="BL47"/>
-      <c r="BM47" s="23"/>
-      <c r="BN47"/>
-      <c r="BO47" s="23"/>
-      <c r="BP47"/>
-      <c r="BQ47" s="23"/>
-      <c r="BR47"/>
-    </row>
-    <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="13">
-        <v>47</v>
-      </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14" t="inlineStr">
-        <is>
-          <t>B0GFWYBKND</t>
-        </is>
-      </c>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48"/>
-      <c r="G48" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>BISSELL CrossWave EdgeFind Wet &amp; Dry Vacuum Cleaner 4136EsPowerful multi-surface pet mess cleanup with ZeroGap Technology,</t>
-        </is>
-      </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0GFWYBKND?psc=1</t>
-        </is>
-      </c>
-      <c r="K48" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61XkhLLFv3L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L48" s="14" t="inlineStr">
-        <is>
-          <t>B0GFWYBKND</t>
-        </is>
-      </c>
-      <c r="M48" s="1"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="15"/>
-      <c r="P48" s="15"/>
-      <c r="Q48" s="16"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="18"/>
-      <c r="T48" s="15"/>
-      <c r="U48" s="16"/>
-      <c r="V48" s="15"/>
-      <c r="W48" s="15"/>
-      <c r="X48" s="15"/>
-      <c r="Y48"/>
-      <c r="Z48" s="19">
-        <v>165.83</v>
-      </c>
-      <c r="AA48"/>
-      <c r="AB48"/>
-      <c r="AC48"/>
-      <c r="AD48" s="20">
-        <v>4</v>
-      </c>
-      <c r="AE48"/>
-      <c r="AF48" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG48" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH48"/>
-      <c r="AI48" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ48"/>
-      <c r="AK48" s="1"/>
-      <c r="AL48" s="20"/>
-      <c r="AM48"/>
-      <c r="AN48" s="13"/>
-      <c r="AO48" s="13"/>
-      <c r="AP48"/>
-      <c r="AQ48" s="20"/>
-      <c r="AR48"/>
-      <c r="AS48"/>
-      <c r="AT48"/>
-      <c r="AU48" s="13"/>
-      <c r="AV48" s="14"/>
-      <c r="AW48" s="13"/>
-      <c r="AX48" s="13"/>
-      <c r="AY48" s="13"/>
-      <c r="AZ48" s="13"/>
-      <c r="BA48" s="13"/>
-      <c r="BB48" s="13"/>
-      <c r="BC48" s="13"/>
-      <c r="BD48" s="13"/>
-      <c r="BE48" s="13"/>
-      <c r="BF48" s="13"/>
-      <c r="BG48" s="13"/>
-      <c r="BH48" s="14"/>
-      <c r="BI48"/>
-      <c r="BJ48"/>
-      <c r="BK48" s="23"/>
-      <c r="BL48"/>
-      <c r="BM48" s="23"/>
-      <c r="BN48"/>
-      <c r="BO48" s="23"/>
-      <c r="BP48"/>
-      <c r="BQ48" s="23"/>
-      <c r="BR48"/>
-    </row>
-    <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="13">
-        <v>48</v>
-      </c>
-      <c r="B49" s="13"/>
-      <c r="C49" s="14" t="inlineStr">
-        <is>
-          <t>B0GQMKR2TW</t>
-        </is>
-      </c>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49"/>
-      <c r="G49" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>Vehiwell Cordless Wet and Dry Vacuum Cleaners3-in-1 Industrial Brushed Vacuum Cleaner, 10L Dry+ 5L Wet Capacity, 13 kPa Suc</t>
-        </is>
-      </c>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0GQMKR2TW?psc=1</t>
-        </is>
-      </c>
-      <c r="K49" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7166tI1-FbL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L49" s="14" t="inlineStr">
-        <is>
-          <t>B0GQMKR2TW</t>
-        </is>
-      </c>
-      <c r="M49" s="1"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="15"/>
-      <c r="P49" s="15"/>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="18"/>
-      <c r="T49" s="15"/>
-      <c r="U49" s="16"/>
-      <c r="V49" s="15"/>
-      <c r="W49" s="15"/>
-      <c r="X49" s="15"/>
-      <c r="Y49"/>
-      <c r="Z49" s="19"/>
-      <c r="AA49"/>
-      <c r="AB49"/>
-      <c r="AC49"/>
-      <c r="AD49" s="20">
-        <v>8</v>
-      </c>
-      <c r="AE49"/>
-      <c r="AF49" s="21">
-        <v>4.6</v>
-      </c>
-      <c r="AG49" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH49"/>
-      <c r="AI49" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ49"/>
-      <c r="AK49" s="1"/>
-      <c r="AL49" s="20"/>
-      <c r="AM49"/>
-      <c r="AN49" s="13"/>
-      <c r="AO49" s="13"/>
-      <c r="AP49"/>
-      <c r="AQ49" s="20"/>
-      <c r="AR49"/>
-      <c r="AS49"/>
-      <c r="AT49"/>
-      <c r="AU49" s="13"/>
-      <c r="AV49" s="14"/>
-      <c r="AW49" s="13"/>
-      <c r="AX49" s="13"/>
-      <c r="AY49" s="13"/>
-      <c r="AZ49" s="13"/>
-      <c r="BA49" s="13"/>
-      <c r="BB49" s="13"/>
-      <c r="BC49" s="13"/>
-      <c r="BD49" s="13"/>
-      <c r="BE49" s="13"/>
-      <c r="BF49" s="13"/>
-      <c r="BG49" s="13"/>
-      <c r="BH49" s="14"/>
-      <c r="BI49"/>
-      <c r="BJ49"/>
-      <c r="BK49" s="23"/>
-      <c r="BL49"/>
-      <c r="BM49" s="23"/>
-      <c r="BN49"/>
-      <c r="BO49" s="23"/>
-      <c r="BP49"/>
-      <c r="BQ49" s="23"/>
-      <c r="BR49"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0H1JPNHB8</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>Vacmaster WD L23 Wet and Dry Vacuum Cleaner 23L, 240V L Class Dust Extractor with 1200W Motor, HEPA 13 Filter, SecureLock Acc</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0H1JPNHB8?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ou0Sb2eIL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0H1JPNHB8</t>
-        </is>
-      </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50"/>
-      <c r="Z50" s="19">
-        <v>74.99</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
-      <c r="AD50" s="20">
-        <v>2</v>
-      </c>
-      <c r="AE50"/>
-      <c r="AF50" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50"/>
-      <c r="AI50" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="20"/>
-      <c r="AM50"/>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="20"/>
-      <c r="AR50"/>
-      <c r="AS50"/>
-      <c r="AT50"/>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50"/>
-      <c r="BJ50"/>
-      <c r="BK50" s="23"/>
-      <c r="BL50"/>
-      <c r="BM50" s="23"/>
-      <c r="BN50"/>
-      <c r="BO50" s="23"/>
-      <c r="BP50"/>
-      <c r="BQ50" s="23"/>
-      <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFYQ6RK2</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>VORACIS 2000W Wet &amp; Dry Vacuum Cleaners20L Stainless Steel | 18000Pa Suction | Blower | HEPA Filter | Car, Home &amp; Garage</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0HFYQ6RK2?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71VX3s1TU3L._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HFYQ6RK2</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="19"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="20"/>
-      <c r="AE51"/>
-      <c r="AF51" s="21"/>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="20"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="20"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11673,198 +10309,153 @@
     <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.co.uk/dp/B083G45ZFH?psc=1"/>
     <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61eFiYsUpUL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B083G45ZFH"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.uk/dp/B083M3VH8K"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.uk/dp/B086QLNK2W"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.uk/dp/B083M3VH8K?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PQHoRU8fL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.uk/dp/B083M3VH8K"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.co.uk/dp/B086QLNK2W"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.uk/dp/B086QLNK2W?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71q6C8hxBzL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.uk/dp/B086QLNK2W"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.co.uk/dp/B098B82K8D"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.co.uk/dp/B086QLNK2W?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71q6C8hxBzL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.co.uk/dp/B086QLNK2W"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.co.uk/dp/B08PC6FMY3"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.co.uk/dp/B098B82K8D?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/714aUu7a7LL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.co.uk/dp/B098B82K8D"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.co.uk/dp/B09CLDC89W"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.co.uk/dp/B08PC6FMY3?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51YRW14YWGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.co.uk/dp/B08PC6FMY3"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.co.uk/dp/B098B82K8D"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.co.uk/dp/B09CLDC89W?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RsLGatnXL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.co.uk/dp/B09CLDC89W"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.co.uk/dp/B09NMKXV6T"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.co.uk/dp/B098B82K8D?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/714aUu7a7LL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.co.uk/dp/B098B82K8D"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.co.uk/dp/B09CLDC89W"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.co.uk/dp/B09NMKXV6T?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Xm8VXEUEL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.co.uk/dp/B09NMKXV6T"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.co.uk/dp/B0B29GRWSR"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.co.uk/dp/B09CLDC89W?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71RsLGatnXL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.co.uk/dp/B09CLDC89W"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.co.uk/dp/B09NMKHHLN"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.co.uk/dp/B0B29GRWSR?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61PIkv1618L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.co.uk/dp/B0B29GRWSR"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.co.uk/dp/B0B4NSXDHS"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.co.uk/dp/B09NMKHHLN?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51Hc6WvljUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.co.uk/dp/B09NMKHHLN"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B09NMKVGNT"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.co.uk/dp/B0B4NSXDHS?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51w4u6UbFuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.co.uk/dp/B0B4NSXDHS"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0BVRQSDT6"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.co.uk/dp/B09NMKVGNT?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51H5+g5PHJL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.co.uk/dp/B09NMKVGNT"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.co.uk/dp/B09NMKXV6T"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.co.uk/dp/B0BVRQSDT6?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61dukUaJDML._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.co.uk/dp/B0BVRQSDT6"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.co.uk/dp/B0CCRTVTWB"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.co.uk/dp/B09NMKXV6T?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Xm8VXEUEL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.co.uk/dp/B09NMKXV6T"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.co.uk/dp/B0B29GRWSR"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.co.uk/dp/B0CCRTVTWB?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Z49VI1-QL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.co.uk/dp/B0CCRTVTWB"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.co.uk/dp/B0CFVBTCGR"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.co.uk/dp/B0B29GRWSR?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61PIkv1618L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.co.uk/dp/B0B29GRWSR"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.co.uk/dp/B0B4NSXDHS"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.co.uk/dp/B0CFVBTCGR?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61G1CZpYmAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.co.uk/dp/B0CFVBTCGR"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.co.uk/dp/B0CLJB2BPC"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.co.uk/dp/B0B4NSXDHS?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51w4u6UbFuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.co.uk/dp/B0B4NSXDHS"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.co.uk/dp/B0BBVY1LB4"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.co.uk/dp/B0CLJB2BPC?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41a9lM1zxaL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.co.uk/dp/B0CLJB2BPC"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.co.uk/dp/B0CMC4GYR8"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.co.uk/dp/B0BBVY1LB4?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61piWzDzo8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.co.uk/dp/B0BBVY1LB4"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.co.uk/dp/B0BGNLL563"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.co.uk/dp/B0CMC4GYR8?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71BKlalgYAL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.co.uk/dp/B0CMC4GYR8"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.co.uk/dp/B0CNGZQD6B"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.co.uk/dp/B0BGNLL563?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71o7Kk6f0YL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.co.uk/dp/B0BGNLL563"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.co.uk/dp/B0BVRQSDT6"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.co.uk/dp/B0CNGZQD6B?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/617n3IksnHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.co.uk/dp/B0CNGZQD6B"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.co.uk/dp/B0CRRG5HVX"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.co.uk/dp/B0BVRQSDT6?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61dukUaJDML._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.co.uk/dp/B0BVRQSDT6"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.co.uk/dp/B0CCRTVTWB"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.co.uk/dp/B0CRRG5HVX?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/615aD+03D3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.co.uk/dp/B0CRRG5HVX"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.co.uk/dp/B0CV5L22GW"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.co.uk/dp/B0CCRTVTWB?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Z49VI1-QL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.co.uk/dp/B0CCRTVTWB"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.co.uk/dp/B0CFVBTCGR"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.co.uk/dp/B0CV5L22GW?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51wD3krd5pL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.co.uk/dp/B0CV5L22GW"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.co.uk/dp/B0CVX37Y93"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.co.uk/dp/B0CFVBTCGR?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61G1CZpYmAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.co.uk/dp/B0CFVBTCGR"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.co.uk/dp/B0CLJB2BPC"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.co.uk/dp/B0CVX37Y93?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71a2hp5QU4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.co.uk/dp/B0CVX37Y93"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.co.uk/dp/B0DJVWGQX1"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.co.uk/dp/B0CLJB2BPC?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/41a9lM1zxaL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.co.uk/dp/B0CLJB2BPC"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.co.uk/dp/B0CMC4GYR8"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.co.uk/dp/B0DJVWGQX1?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51w6h2F2dwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.co.uk/dp/B0DJVWGQX1"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.co.uk/dp/B0DPGJ8NTW"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.co.uk/dp/B0CMC4GYR8?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71BKlalgYAL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.co.uk/dp/B0CMC4GYR8"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.co.uk/dp/B0CNGZQD6B"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.co.uk/dp/B0DPGJ8NTW?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51hO3VO8sgL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.co.uk/dp/B0DPGJ8NTW"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.co.uk/dp/B0DWFZ1GWR"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.co.uk/dp/B0CNGZQD6B?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/617n3IksnHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.co.uk/dp/B0CNGZQD6B"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.co.uk/dp/B0CNRT2132"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.co.uk/dp/B0DWFZ1GWR?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71W7kv60oTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.co.uk/dp/B0DWFZ1GWR"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.co.uk/dp/B0F54PJHNV"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.co.uk/dp/B0CNRT2132?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ooDYkz3gL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.co.uk/dp/B0CNRT2132"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.co.uk/dp/B0CRRG5HVX"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.co.uk/dp/B0F54PJHNV?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71jUHr7KHeL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.co.uk/dp/B0F54PJHNV"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.co.uk/dp/B0F7JY3BHY"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.co.uk/dp/B0CRRG5HVX?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/615aD+03D3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.co.uk/dp/B0CRRG5HVX"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.co.uk/dp/B0CV5L22GW"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.co.uk/dp/B0F7JY3BHY?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61L+f7jvShL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.co.uk/dp/B0F7JY3BHY"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.co.uk/dp/B0FLJDDWQM"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.co.uk/dp/B0CV5L22GW?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51wD3krd5pL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.co.uk/dp/B0CV5L22GW"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.co.uk/dp/B0CVX37Y93"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.co.uk/dp/B0FLJDDWQM?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61PF6yf8UEL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.co.uk/dp/B0FLJDDWQM"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.co.uk/dp/B0FQJS7TKK"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.co.uk/dp/B0CVX37Y93?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71a2hp5QU4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.co.uk/dp/B0CVX37Y93"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.co.uk/dp/B0DJVWGQX1"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.co.uk/dp/B0FQJS7TKK?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71A25KhrmQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.co.uk/dp/B0FQJS7TKK"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.co.uk/dp/B0FWQK9J67"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.co.uk/dp/B0DJVWGQX1?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51w6h2F2dwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.co.uk/dp/B0DJVWGQX1"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.co.uk/dp/B0DPGJ8NTW"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.co.uk/dp/B0FWQK9J67?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71QQSYxzFRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.co.uk/dp/B0FWQK9J67"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.co.uk/dp/B0DPGJ8NTW?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51hO3VO8sgL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.co.uk/dp/B0DPGJ8NTW"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.co.uk/dp/B0DWFZ1GWR"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61mDGPAy6RL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.co.uk/dp/B0G2KSRMM3"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.co.uk/dp/B0DWFZ1GWR?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71W7kv60oTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.co.uk/dp/B0DWFZ1GWR"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.co.uk/dp/B0F54PJHNV"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.co.uk/dp/B0G2KSRMM3?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61zSPayhZhL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.co.uk/dp/B0G2KSRMM3"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.co.uk/dp/B0G4BQN2R8"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.co.uk/dp/B0F54PJHNV?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71jUHr7KHeL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.co.uk/dp/B0F54PJHNV"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.co.uk/dp/B0F7JY3BHY"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.co.uk/dp/B0G4BQN2R8?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Hnmdt4DPL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.co.uk/dp/B0G4BQN2R8"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.co.uk/dp/B0GFWYBKND"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.co.uk/dp/B0F7JY3BHY?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61L+f7jvShL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.co.uk/dp/B0F7JY3BHY"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.co.uk/dp/B0FLJDDWQM"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.co.uk/dp/B0GFWYBKND?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61XkhLLFv3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.co.uk/dp/B0GFWYBKND"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.co.uk/dp/B0GQMKR2TW"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.co.uk/dp/B0FLJDDWQM?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61PF6yf8UEL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.co.uk/dp/B0FLJDDWQM"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B0FQJS7TKK"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.co.uk/dp/B0GQMKR2TW?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7166tI1-FbL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.co.uk/dp/B0GQMKR2TW"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B0HFYQ6RK2"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.uk/dp/B0FQJS7TKK?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71A25KhrmQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.uk/dp/B0FQJS7TKK"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B0FWQK9J67"/>
-    <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B0FWQK9J67?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71QQSYxzFRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.uk/dp/B0FWQK9J67"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J"/>
-    <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61mDGPAy6RL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.uk/dp/B0FZDZCB3J"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.co.uk/dp/B0G2KSRMM3"/>
-    <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.co.uk/dp/B0G2KSRMM3?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61zSPayhZhL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.co.uk/dp/B0G2KSRMM3"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.co.uk/dp/B0G4BQN2R8"/>
-    <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.co.uk/dp/B0G4BQN2R8?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Hnmdt4DPL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.co.uk/dp/B0G4BQN2R8"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.co.uk/dp/B0G7T8PCM4"/>
-    <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.co.uk/dp/B0G7T8PCM4?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71JgbgU+z-L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.co.uk/dp/B0G7T8PCM4"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.co.uk/dp/B0GFWYBKND"/>
-    <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.uk/dp/B0GFWYBKND?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61XkhLLFv3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0GFWYBKND"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.uk/dp/B0GQMKR2TW"/>
-    <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.uk/dp/B0GQMKR2TW?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7166tI1-FbL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.uk/dp/B0GQMKR2TW"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.co.uk/dp/B0H1JPNHB8"/>
-    <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.co.uk/dp/B0H1JPNHB8?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ou0Sb2eIL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.co.uk/dp/B0H1JPNHB8"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.co.uk/dp/B0HFYQ6RK2"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.co.uk/dp/B0HFYQ6RK2?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71VX3s1TU3L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.co.uk/dp/B0HFYQ6RK2"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.uk/dp/B0HFYQ6RK2?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71VX3s1TU3L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.uk/dp/B0HFYQ6RK2"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId206"/>
 </worksheet>
 </file>
 
